--- a/data/trans_dic/IP16A112_2023R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A112_2023R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre</t>
+          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 54,42</t>
+          <t>5,39; 54,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,68; 65,39</t>
+          <t>23,27; 69,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 52,78</t>
+          <t>18,51; 54,65</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,96; 52,44</t>
+          <t>20,46; 52,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,9; 48,76</t>
+          <t>33,04; 49,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,8; 46,77</t>
+          <t>27,35; 46,69</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,2; 61,98</t>
+          <t>36,94; 62,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,75; 64,5</t>
+          <t>39,36; 66,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,93; 59,68</t>
+          <t>41,44; 59,99</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,77; 49,62</t>
+          <t>24,25; 50,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,26; 50,85</t>
+          <t>37,85; 51,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,87; 46,96</t>
+          <t>31,54; 47,59</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6975</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10868</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>821; 8226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3646; 10827</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5719; 16885</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>46876</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48536</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>95411</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>25061; 63712</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39655; 58907</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>66336; 113233</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>20748</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24585</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45334</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>15384; 26010</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18509; 31237</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>36741; 53185</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80096</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>151613</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>43497; 90425</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69163; 93943</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>114202; 172312</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A112_2023R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A112_2023R-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 54,01</t>
+          <t>4,29; 52,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,27; 69,11</t>
+          <t>23,55; 66,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 54,65</t>
+          <t>18,08; 53,51</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,46; 52,02</t>
+          <t>20,71; 52,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,04; 49,08</t>
+          <t>32,86; 48,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,35; 46,69</t>
+          <t>24,85; 46,52</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,94; 62,46</t>
+          <t>37,39; 62,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,36; 66,44</t>
+          <t>39,67; 65,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,44; 59,99</t>
+          <t>42,12; 60,31</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,25; 50,42</t>
+          <t>25,01; 50,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,85; 51,42</t>
+          <t>37,19; 50,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,54; 47,59</t>
+          <t>32,59; 47,74</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>821; 8226</t>
+          <t>654; 7991</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3646; 10827</t>
+          <t>3690; 10454</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5719; 16885</t>
+          <t>5585; 16534</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25061; 63712</t>
+          <t>25369; 63854</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39655; 58907</t>
+          <t>39441; 58085</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66336; 113233</t>
+          <t>60254; 112818</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15384; 26010</t>
+          <t>15572; 26154</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18509; 31237</t>
+          <t>18654; 31011</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36741; 53185</t>
+          <t>37343; 53471</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43497; 90425</t>
+          <t>44851; 90132</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69163; 93943</t>
+          <t>67953; 92577</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114202; 172312</t>
+          <t>118007; 172866</t>
         </is>
       </c>
     </row>
